--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -134,10 +134,51 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="0"/>
       </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="0"/>
@@ -145,58 +186,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -238,51 +227,27 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -329,17 +294,31 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -349,22 +328,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -373,40 +352,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -740,152 +710,152 @@
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="19"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="23">
+      <c r="C4" s="20">
         <v>1</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="24">
+      <c r="B5" s="9"/>
+      <c r="C5" s="21">
         <v>2</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="19"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="15">
+      <c r="C6" s="21">
         <v>3</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="15">
+      <c r="B7" s="9"/>
+      <c r="C7" s="21">
         <v>4</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="19"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="15">
+      <c r="C8" s="12">
         <v>5</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="15">
+      <c r="B9" s="9"/>
+      <c r="C9" s="12">
         <v>6</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="15">
+      <c r="C10" s="12">
         <v>7</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
-      <c r="C11" s="15">
+      <c r="C11" s="12">
         <v>8</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="15">
+      <c r="C12" s="12">
         <v>9</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
-      <c r="C13" s="15">
+      <c r="C13" s="12">
         <v>10</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-      <c r="C14" s="15">
+      <c r="C14" s="12">
         <v>11</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
-      <c r="C15" s="15">
+      <c r="C15" s="12">
         <v>12</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="15">
+      <c r="C16" s="12">
         <v>13</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="17"/>
-      <c r="C17" s="16">
+      <c r="B17" s="14"/>
+      <c r="C17" s="13">
         <v>14</v>
       </c>
       <c r="D17" s="11"/>
@@ -894,30 +864,33 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="5"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -311,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -346,12 +346,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -377,6 +371,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -387,11 +390,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF99"/>
       <color rgb="FFCCCCFF"/>
+      <color rgb="FFFFCCCC"/>
       <color rgb="FF66FF99"/>
       <color rgb="FF99FF99"/>
-      <color rgb="FFFFFF99"/>
-      <color rgb="FFFFCCCC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -710,7 +713,7 @@
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="9"/>
@@ -724,9 +727,9 @@
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16"/>
+      <c r="A4" s="14"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="20">
+      <c r="C4" s="18">
         <v>1</v>
       </c>
       <c r="D4" s="6"/>
@@ -734,11 +737,11 @@
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="15" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <v>2</v>
       </c>
       <c r="D5" s="7"/>
@@ -746,9 +749,9 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16"/>
+      <c r="A6" s="14"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="21">
+      <c r="C6" s="19">
         <v>3</v>
       </c>
       <c r="D6" s="7"/>
@@ -756,11 +759,11 @@
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="16" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="21">
+      <c r="C7" s="19">
         <v>4</v>
       </c>
       <c r="D7" s="7"/>
@@ -768,9 +771,9 @@
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="12">
+      <c r="C8" s="19">
         <v>5</v>
       </c>
       <c r="D8" s="7"/>
@@ -778,11 +781,11 @@
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="9"/>
-      <c r="C9" s="12">
+      <c r="C9" s="21">
         <v>6</v>
       </c>
       <c r="D9" s="7"/>
@@ -792,7 +795,7 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="12">
+      <c r="C10" s="22">
         <v>7</v>
       </c>
       <c r="D10" s="7"/>
@@ -801,7 +804,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
-      <c r="C11" s="12">
+      <c r="C11" s="22">
         <v>8</v>
       </c>
       <c r="D11" s="7"/>
@@ -810,7 +813,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="12">
+      <c r="C12" s="22">
         <v>9</v>
       </c>
       <c r="D12" s="7"/>
@@ -819,16 +822,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
-      <c r="C13" s="12">
+      <c r="C13" s="22">
         <v>10</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-      <c r="C14" s="12">
+      <c r="C14" s="22">
         <v>11</v>
       </c>
       <c r="D14" s="11"/>
@@ -837,7 +840,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
-      <c r="C15" s="12">
+      <c r="C15" s="22">
         <v>12</v>
       </c>
       <c r="D15" s="11"/>
@@ -846,7 +849,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="12">
+      <c r="C16" s="22">
         <v>13</v>
       </c>
       <c r="D16" s="11"/>
@@ -854,8 +857,8 @@
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="14"/>
-      <c r="C17" s="13">
+      <c r="B17" s="12"/>
+      <c r="C17" s="23">
         <v>14</v>
       </c>
       <c r="D17" s="11"/>

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Адміністрування обчислювальних комплексів</t>
   </si>
@@ -28,10 +28,13 @@
     <t>в процессе</t>
   </si>
   <si>
-    <t>готов док и лр</t>
+    <t>заучила, готово</t>
   </si>
   <si>
-    <t>заучила, готово</t>
+    <t>т пзда</t>
+  </si>
+  <si>
+    <t>готов документ</t>
   </si>
 </sst>
 </file>
@@ -311,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,12 +331,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -370,9 +367,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -380,6 +374,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -390,8 +396,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCCCFF"/>
       <color rgb="FFFFFF99"/>
-      <color rgb="FFCCCCFF"/>
       <color rgb="FFFFCCCC"/>
       <color rgb="FF66FF99"/>
       <color rgb="FF99FF99"/>
@@ -713,180 +719,182 @@
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="14"/>
+      <c r="A4" s="12"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="18">
+      <c r="C4" s="16">
         <v>1</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="19">
+      <c r="B5" s="7"/>
+      <c r="C5" s="17">
         <v>2</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="14"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="19">
+      <c r="C6" s="17">
         <v>3</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="17">
         <v>4</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="19">
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="12"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="17">
+        <v>5</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="14"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="19">
-        <v>5</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="21">
+      <c r="B9" s="7"/>
+      <c r="C9" s="17">
         <v>6</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="22">
+      <c r="C10" s="17">
         <v>7</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
-      <c r="C11" s="22">
+      <c r="C11" s="17">
         <v>8</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="22">
+      <c r="C12" s="17">
         <v>9</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
-      <c r="C13" s="22">
+      <c r="C13" s="17">
         <v>10</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-      <c r="C14" s="22">
+      <c r="C14" s="17">
         <v>11</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
-      <c r="C15" s="22">
+      <c r="C15" s="18">
         <v>12</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="22">
+      <c r="C16" s="19">
         <v>13</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="12"/>
-      <c r="C17" s="23">
+      <c r="B17" s="10"/>
+      <c r="C17" s="20">
         <v>14</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -314,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -365,9 +365,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -396,9 +393,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFFFFF99"/>
       <color rgb="FFCCCCFF"/>
-      <color rgb="FFFFFF99"/>
-      <color rgb="FFFFCCCC"/>
       <color rgb="FF66FF99"/>
       <color rgb="FF99FF99"/>
     </mruColors>
@@ -740,8 +737,8 @@
       <c r="C4" s="16">
         <v>1</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -752,8 +749,8 @@
       <c r="C5" s="17">
         <v>2</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -762,8 +759,8 @@
       <c r="C6" s="17">
         <v>3</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -774,8 +771,8 @@
       <c r="C7" s="17">
         <v>4</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -784,8 +781,8 @@
       <c r="C8" s="17">
         <v>5</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -796,8 +793,8 @@
       <c r="C9" s="17">
         <v>6</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -806,8 +803,8 @@
       <c r="C10" s="17">
         <v>7</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -815,8 +812,8 @@
       <c r="C11" s="17">
         <v>8</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -824,8 +821,8 @@
       <c r="C12" s="17">
         <v>9</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -833,17 +830,17 @@
       <c r="C13" s="17">
         <v>10</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-      <c r="C14" s="17">
+      <c r="C14" s="18">
         <v>11</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -851,26 +848,26 @@
       <c r="C15" s="18">
         <v>12</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="19">
+      <c r="C16" s="18">
         <v>13</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="10"/>
-      <c r="C17" s="20">
+      <c r="C17" s="19">
         <v>14</v>
       </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -64,7 +64,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,6 +101,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -314,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -383,6 +389,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -818,7 +827,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="17">
+      <c r="C12" s="24">
         <v>9</v>
       </c>
       <c r="D12" s="21"/>
@@ -827,7 +836,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
-      <c r="C13" s="17">
+      <c r="C13" s="24">
         <v>10</v>
       </c>
       <c r="D13" s="22"/>

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -64,7 +64,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,12 +101,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -320,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -389,9 +383,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -402,9 +393,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCCCFF"/>
       <color rgb="FFFFCCCC"/>
       <color rgb="FFFFFF99"/>
-      <color rgb="FFCCCCFF"/>
       <color rgb="FF66FF99"/>
       <color rgb="FF99FF99"/>
     </mruColors>
@@ -827,7 +818,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="24">
+      <c r="C12" s="17">
         <v>9</v>
       </c>
       <c r="D12" s="21"/>
@@ -836,7 +827,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
-      <c r="C13" s="24">
+      <c r="C13" s="17">
         <v>10</v>
       </c>
       <c r="D13" s="22"/>
@@ -845,7 +836,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>11</v>
       </c>
       <c r="D14" s="23"/>

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -845,7 +845,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>12</v>
       </c>
       <c r="D15" s="23"/>

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -64,7 +64,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,6 +101,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -367,12 +373,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -383,6 +383,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -737,8 +743,8 @@
       <c r="C4" s="16">
         <v>1</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -749,8 +755,8 @@
       <c r="C5" s="17">
         <v>2</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -759,8 +765,8 @@
       <c r="C6" s="17">
         <v>3</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -771,8 +777,8 @@
       <c r="C7" s="17">
         <v>4</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -781,8 +787,8 @@
       <c r="C8" s="17">
         <v>5</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -793,8 +799,8 @@
       <c r="C9" s="17">
         <v>6</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -803,8 +809,8 @@
       <c r="C10" s="17">
         <v>7</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -812,8 +818,8 @@
       <c r="C11" s="17">
         <v>8</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -821,8 +827,8 @@
       <c r="C12" s="17">
         <v>9</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -830,8 +836,8 @@
       <c r="C13" s="17">
         <v>10</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -839,8 +845,8 @@
       <c r="C14" s="17">
         <v>11</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -848,26 +854,26 @@
       <c r="C15" s="17">
         <v>12</v>
       </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="18">
+      <c r="C16" s="22">
         <v>13</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="10"/>
-      <c r="C17" s="19">
+      <c r="C17" s="23">
         <v>14</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -383,9 +383,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -860,7 +857,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="22">
+      <c r="C16" s="17">
         <v>13</v>
       </c>
       <c r="D16" s="21"/>
@@ -869,7 +866,7 @@
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="10"/>
-      <c r="C17" s="23">
+      <c r="C17" s="22">
         <v>14</v>
       </c>
       <c r="D17" s="21"/>

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -41,7 +41,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,8 +63,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,12 +107,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -385,7 +385,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -14,12 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Адміністрування обчислювальних комплексів</t>
-  </si>
-  <si>
-    <t>Моделювання та аналіз програмного забезпечення</t>
   </si>
   <si>
     <t>не готово</t>
@@ -35,6 +32,13 @@
   </si>
   <si>
     <t>готов документ</t>
+  </si>
+  <si>
+    <t>курси</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моделювання та аналіз
+програмного забезпечення </t>
   </si>
 </sst>
 </file>
@@ -108,7 +112,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -316,11 +320,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -343,9 +387,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -382,11 +423,44 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -718,183 +792,203 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:6" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="15">
+        <v>1</v>
+      </c>
+      <c r="D4" s="29">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="16">
+        <v>2</v>
+      </c>
+      <c r="D5" s="30">
+        <v>2</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="16">
+        <v>3</v>
+      </c>
+      <c r="D6" s="30">
+        <v>3</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="16">
-        <v>1</v>
-      </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="16">
+        <v>4</v>
+      </c>
+      <c r="D7" s="30">
+        <v>4</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="16">
+        <v>5</v>
+      </c>
+      <c r="D8" s="30">
+        <v>5</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="17">
-        <v>2</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="12"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="17">
-        <v>3</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="17">
-        <v>4</v>
-      </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="12"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="17">
-        <v>5</v>
-      </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="17">
+      <c r="D9" s="30">
         <v>6</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>7</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="D10" s="30">
+        <v>7</v>
+      </c>
+      <c r="E10" s="18"/>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>8</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="D11" s="30">
+        <v>8</v>
+      </c>
+      <c r="E11" s="18"/>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>9</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="D12" s="30">
+        <v>9</v>
+      </c>
+      <c r="E12" s="18"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="2"/>
-      <c r="C13" s="17">
+      <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="D13" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="19"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-      <c r="C14" s="17">
+      <c r="C14" s="16">
         <v>11</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
-      <c r="C15" s="17">
+      <c r="C15" s="16">
         <v>12</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="17">
+      <c r="C16" s="16">
         <v>13</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="10"/>
-      <c r="C17" s="22">
+      <c r="B17" s="9"/>
+      <c r="C17" s="20">
         <v>14</v>
       </c>
       <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Адміністрування обчислювальних комплексів</t>
   </si>
@@ -39,6 +39,9 @@
   <si>
     <t xml:space="preserve">Моделювання та аналіз
 програмного забезпечення </t>
+  </si>
+  <si>
+    <t>Диплом</t>
   </si>
 </sst>
 </file>
@@ -112,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -214,32 +217,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -307,17 +284,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -364,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -381,10 +347,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -396,7 +362,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -408,13 +374,34 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -423,44 +410,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -797,13 +760,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="24" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="28" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="3"/>
@@ -814,10 +777,12 @@
       <c r="C4" s="15">
         <v>1</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="25">
         <v>1</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="25">
+        <v>1</v>
+      </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -828,10 +793,12 @@
       <c r="C5" s="16">
         <v>2</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="26">
         <v>2</v>
       </c>
-      <c r="E5" s="18"/>
+      <c r="E5" s="26">
+        <v>2</v>
+      </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -840,10 +807,12 @@
       <c r="C6" s="16">
         <v>3</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <v>3</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="26">
+        <v>3</v>
+      </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -854,10 +823,12 @@
       <c r="C7" s="16">
         <v>4</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="26">
         <v>4</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="26">
+        <v>4</v>
+      </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -866,10 +837,12 @@
       <c r="C8" s="16">
         <v>5</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <v>5</v>
       </c>
-      <c r="E8" s="18"/>
+      <c r="E8" s="26">
+        <v>5</v>
+      </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -880,10 +853,12 @@
       <c r="C9" s="16">
         <v>6</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="26">
         <v>6</v>
       </c>
-      <c r="E9" s="18"/>
+      <c r="E9" s="26">
+        <v>6</v>
+      </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -892,10 +867,12 @@
       <c r="C10" s="16">
         <v>7</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="26">
         <v>7</v>
       </c>
-      <c r="E10" s="18"/>
+      <c r="E10" s="26">
+        <v>7</v>
+      </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -903,21 +880,25 @@
       <c r="C11" s="16">
         <v>8</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="26">
         <v>8</v>
       </c>
-      <c r="E11" s="18"/>
+      <c r="E11" s="26">
+        <v>8</v>
+      </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="2"/>
       <c r="C12" s="16">
         <v>9</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="26">
         <v>9</v>
       </c>
-      <c r="E12" s="18"/>
+      <c r="E12" s="26">
+        <v>9</v>
+      </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -925,10 +906,12 @@
       <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="19"/>
+      <c r="E13" s="31" t="s">
+        <v>8</v>
+      </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -936,8 +919,8 @@
       <c r="C14" s="16">
         <v>11</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="22"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -945,8 +928,8 @@
       <c r="C15" s="16">
         <v>12</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -954,17 +937,17 @@
       <c r="C16" s="16">
         <v>13</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="24"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="9"/>
-      <c r="C17" s="20">
+      <c r="C17" s="17">
         <v>14</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="23"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -972,7 +955,7 @@
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">

--- a/Готовность.xlsx
+++ b/Готовность.xlsx
@@ -422,7 +422,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -433,9 +433,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF99"/>
       <color rgb="FFCCCCFF"/>
       <color rgb="FFFFCCCC"/>
-      <color rgb="FFFFFF99"/>
       <color rgb="FF66FF99"/>
       <color rgb="FF99FF99"/>
     </mruColors>
